--- a/utils/monday_sprint_sprint_2023-09.xlsx
+++ b/utils/monday_sprint_sprint_2023-09.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="430" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="118">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Abertura</t>
+    <t>Entrada Sprint</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,6 +51,9 @@
     <t>Status</t>
   </si>
   <si>
+    <t>SLA (15 dias)</t>
+  </si>
+  <si>
     <t>Semana</t>
   </si>
   <si>
@@ -60,36 +63,60 @@
     <t>17403</t>
   </si>
   <si>
-    <t>Sprint 2023-09</t>
+    <t>Setor não informado</t>
   </si>
   <si>
     <t>Melhoria</t>
   </si>
   <si>
+    <t>Categoria não informada</t>
+  </si>
+  <si>
+    <t>Vida útil dos modelos.</t>
+  </si>
+  <si>
+    <t>Média</t>
+  </si>
+  <si>
+    <t>Solicitante não informado</t>
+  </si>
+  <si>
+    <t>Equipe não informada</t>
+  </si>
+  <si>
+    <t>16/02/2023</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Vida útil dos modelos.</t>
-  </si>
-  <si>
-    <t>Média</t>
-  </si>
-  <si>
     <t>Feito</t>
   </si>
   <si>
+    <t>Não</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
     <t>19181 [não fechar]</t>
   </si>
   <si>
     <t>Novo processo de OTFs de Serviços/Ferramentais</t>
   </si>
   <si>
+    <t>23/03/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
+    <t>Março</t>
+  </si>
+  <si>
     <t>19203</t>
   </si>
   <si>
@@ -108,15 +135,24 @@
     <t>Alta</t>
   </si>
   <si>
+    <t>24/03/2023</t>
+  </si>
+  <si>
     <t>19473</t>
   </si>
   <si>
     <t>Ajustes dos Créditos Presumidos de ICMS informados na EFD-ICMS/IPI</t>
   </si>
   <si>
+    <t>06/04/2023</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
+    <t>Abril</t>
+  </si>
+  <si>
     <t>19560</t>
   </si>
   <si>
@@ -135,6 +171,9 @@
     <t>Incluir número da SIC fluxo de caixa</t>
   </si>
   <si>
+    <t>24/04/2023</t>
+  </si>
+  <si>
     <t>4366804709</t>
   </si>
   <si>
@@ -147,12 +186,18 @@
     <t>Não definida</t>
   </si>
   <si>
+    <t>25/04/2023</t>
+  </si>
+  <si>
     <t>19402</t>
   </si>
   <si>
     <t>Relatório Razão Crítica &gt; Adequação do Lay Out</t>
   </si>
   <si>
+    <t>18/04/2023</t>
+  </si>
+  <si>
     <t>19832</t>
   </si>
   <si>
@@ -276,7 +321,7 @@
     <t>Distribuição por Tipo</t>
   </si>
   <si>
-    <t>Cumprimento SLA</t>
+    <t>Cumprimento SLA (15 dias)</t>
   </si>
   <si>
     <t>Status Final</t>
@@ -294,10 +339,10 @@
     <t>Sim</t>
   </si>
   <si>
-    <t>Não</t>
-  </si>
-  <si>
     <t>A fazer</t>
+  </si>
+  <si>
+    <t>Abertos</t>
   </si>
   <si>
     <t>Impedimento</t>
@@ -738,7 +783,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N25"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -748,13 +793,15 @@
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="25" customWidth="1"/>
     <col min="9" max="9" width="20" customWidth="1"/>
-    <col min="10" max="11" width="14" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="16" customWidth="1"/>
-    <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -797,1061 +844,1136 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="I12" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="J13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O17" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O19" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O20" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N21" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O21" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="K22" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="2" t="s">
+      <c r="H23" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="K23" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N23" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N24" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="O24" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="N25" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N10" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="O25" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N11" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L20" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N20" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N21" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L22" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M22" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N23" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L24" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="K25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L25" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N25" s="2" t="s">
-        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -1867,23 +1989,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>73</v>
+        <v>88</v>
       </c>
       <c r="B2" t="s">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -1891,16 +2013,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1911,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>19.17</v>
+        <v>0</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -1919,12 +2041,12 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J22" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K22">
         <v>24</v>
@@ -1932,7 +2054,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -1940,7 +2062,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -1971,12 +2093,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="B2">
         <v>24</v>
@@ -1990,7 +2112,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>19.17</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2000,60 +2122,60 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>24</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10">
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="K10">
         <v>0</v>
       </c>
       <c r="M10" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N10">
         <v>24</v>
       </c>
       <c r="P10" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="Q10">
         <v>3</v>
@@ -2061,31 +2183,31 @@
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="H11">
         <v>7</v>
       </c>
       <c r="J11" t="s">
-        <v>93</v>
+        <v>26</v>
       </c>
       <c r="K11">
         <v>24</v>
       </c>
       <c r="M11" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="Q11">
         <v>3</v>
@@ -2093,25 +2215,31 @@
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="E12">
         <v>3</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H12">
         <v>14</v>
       </c>
+      <c r="J12" t="s">
+        <v>109</v>
+      </c>
+      <c r="K12">
+        <v>0</v>
+      </c>
       <c r="M12" t="s">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="Q12">
         <v>18</v>
@@ -2119,19 +2247,19 @@
     </row>
     <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>61</v>
+        <v>76</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2139,13 +2267,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>82</v>
+        <v>97</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2153,7 +2281,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2161,7 +2289,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>99</v>
+        <v>114</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2169,7 +2297,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2177,7 +2305,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -2188,7 +2316,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2196,142 +2324,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F21" s="2">
         <v>0</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F22" s="2">
         <v>0</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2">
         <v>0</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F24" s="2">
         <v>0</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F25" s="2">
         <v>0</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F26" s="2">
         <v>0</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F27" s="2">
         <v>0</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F28" s="2">
         <v>0</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F29" s="2">
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F30" s="2">
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>45</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2023-09.xlsx
+++ b/utils/monday_sprint_sprint_2023-09.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="128">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>17403</t>
+    <t>3999916662</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>16/02/2023</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>04/05/2023</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>19181 [não fechar]</t>
+    <t>4194109523</t>
   </si>
   <si>
     <t>Novo processo de OTFs de Serviços/Ferramentais</t>
@@ -111,19 +111,22 @@
     <t>23/03/2023</t>
   </si>
   <si>
+    <t>06/05/2023</t>
+  </si>
+  <si>
     <t>Semana 4</t>
   </si>
   <si>
     <t>Março</t>
   </si>
   <si>
-    <t>19203</t>
+    <t>4194246525</t>
   </si>
   <si>
     <t>Corrigir Tipo de OTF - QVIEW</t>
   </si>
   <si>
-    <t>16359</t>
+    <t>4201075722</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -138,7 +141,10 @@
     <t>24/03/2023</t>
   </si>
   <si>
-    <t>19473</t>
+    <t>05/05/2023</t>
+  </si>
+  <si>
+    <t>4271740793</t>
   </si>
   <si>
     <t>Ajustes dos Créditos Presumidos de ICMS informados na EFD-ICMS/IPI</t>
@@ -147,25 +153,34 @@
     <t>06/04/2023</t>
   </si>
   <si>
+    <t>02/05/2023</t>
+  </si>
+  <si>
     <t>Semana 1</t>
   </si>
   <si>
     <t>Abril</t>
   </si>
   <si>
-    <t>19560</t>
+    <t>4272068422</t>
   </si>
   <si>
     <t>Cadastro conta do portador.</t>
   </si>
   <si>
-    <t>19378</t>
+    <t>30/04/2023</t>
+  </si>
+  <si>
+    <t>4273112307</t>
   </si>
   <si>
     <t>Integrar ao Sistema de Faturamento</t>
   </si>
   <si>
-    <t>19854</t>
+    <t>23/04/2023</t>
+  </si>
+  <si>
+    <t>4358907785</t>
   </si>
   <si>
     <t>Incluir número da SIC fluxo de caixa</t>
@@ -189,7 +204,10 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>19402</t>
+    <t>07/05/2023</t>
+  </si>
+  <si>
+    <t>4326572292</t>
   </si>
   <si>
     <t>Relatório Razão Crítica &gt; Adequação do Lay Out</t>
@@ -198,31 +216,31 @@
     <t>18/04/2023</t>
   </si>
   <si>
-    <t>19832</t>
+    <t>4359007221</t>
   </si>
   <si>
     <t>Alteração / Acesso Orçamento</t>
   </si>
   <si>
-    <t>19753</t>
+    <t>4359131501</t>
   </si>
   <si>
     <t>Alteração Sistema Pré-produtivo</t>
   </si>
   <si>
-    <t>9107</t>
+    <t>4359183272</t>
   </si>
   <si>
     <t>Devolutiva revisão de fluxo - Lista de revisões pendentes.</t>
   </si>
   <si>
-    <t>19801</t>
+    <t>4359056349</t>
   </si>
   <si>
     <t>Abertura de Pendência Automática</t>
   </si>
   <si>
-    <t>19826</t>
+    <t>4359031514</t>
   </si>
   <si>
     <t>Sistema Invoice- Obrigatoriedade de Campo</t>
@@ -231,16 +249,19 @@
     <t>4366804842</t>
   </si>
   <si>
+    <t>4359671213</t>
+  </si>
+  <si>
     <t>Criar tela de conferência entre nota fiscal, recibo e romaneio</t>
   </si>
   <si>
-    <t>14430</t>
+    <t>4366479758</t>
   </si>
   <si>
     <t>Tela de conferencia de pre embarque</t>
   </si>
   <si>
-    <t>18631</t>
+    <t>4364264807</t>
   </si>
   <si>
     <t>Novo Recurso</t>
@@ -252,25 +273,31 @@
     <t>4366804988</t>
   </si>
   <si>
-    <t>19784</t>
+    <t>4329927494</t>
   </si>
   <si>
     <t>Alteração Sistema SIC Web</t>
   </si>
   <si>
-    <t>19538</t>
+    <t>01/05/2023</t>
+  </si>
+  <si>
+    <t>4359150909</t>
   </si>
   <si>
     <t>Incluir um campo de busca pelo número da pré-lista</t>
   </si>
   <si>
-    <t>19883</t>
+    <t>27/04/2023</t>
+  </si>
+  <si>
+    <t>4363575918</t>
   </si>
   <si>
     <t>Alteração layout SIC e saldo de orçamento</t>
   </si>
   <si>
-    <t>19885</t>
+    <t>4366747078</t>
   </si>
   <si>
     <t>Preenchimento de SIC x Ordem criada com Divergência</t>
@@ -282,7 +309,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2023-09</t>
+    <t>Fev/2023</t>
   </si>
   <si>
     <t>Base</t>
@@ -346,6 +373,9 @@
   </si>
   <si>
     <t>Impedimento</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
   </si>
   <si>
     <t>Baixa</t>
@@ -927,7 +957,7 @@
         <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -936,15 +966,15 @@
         <v>26</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -956,10 +986,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -983,33 +1013,33 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>21</v>
@@ -1018,10 +1048,10 @@
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1030,15 +1060,15 @@
         <v>26</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1050,13 +1080,13 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>21</v>
@@ -1065,10 +1095,10 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1077,15 +1107,15 @@
         <v>26</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
@@ -1097,10 +1127,10 @@
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1112,10 +1142,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1124,33 +1154,33 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>21</v>
@@ -1159,10 +1189,10 @@
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1171,15 +1201,15 @@
         <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1191,10 +1221,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1206,7 +1236,7 @@
         <v>22</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>24</v>
@@ -1218,33 +1248,33 @@
         <v>26</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O9" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>21</v>
@@ -1253,10 +1283,10 @@
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1265,15 +1295,15 @@
         <v>26</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1285,13 +1315,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>21</v>
@@ -1300,10 +1330,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1315,12 +1345,12 @@
         <v>27</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1332,10 +1362,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1347,10 +1377,10 @@
         <v>22</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1359,15 +1389,15 @@
         <v>26</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1379,10 +1409,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1394,10 +1424,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1406,15 +1436,15 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1426,10 +1456,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1441,10 +1471,10 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L14" s="2" t="s">
         <v>25</v>
@@ -1453,15 +1483,15 @@
         <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1473,10 +1503,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1488,10 +1518,10 @@
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1500,15 +1530,15 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
@@ -1520,10 +1550,10 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1535,10 +1565,10 @@
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1547,33 +1577,33 @@
         <v>26</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>21</v>
@@ -1582,10 +1612,10 @@
         <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L17" s="2" t="s">
         <v>25</v>
@@ -1594,15 +1624,15 @@
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
@@ -1614,10 +1644,10 @@
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -1629,10 +1659,10 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
@@ -1641,30 +1671,30 @@
         <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1676,10 +1706,10 @@
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1688,30 +1718,30 @@
         <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O19" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1723,10 +1753,10 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="L20" s="2" t="s">
         <v>25</v>
@@ -1735,33 +1765,33 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
@@ -1770,10 +1800,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>63</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -1782,15 +1812,15 @@
         <v>26</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
@@ -1802,13 +1832,13 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>21</v>
@@ -1817,10 +1847,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -1832,12 +1862,12 @@
         <v>27</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -1849,10 +1879,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -1864,10 +1894,10 @@
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -1876,15 +1906,15 @@
         <v>26</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
@@ -1896,13 +1926,13 @@
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>21</v>
@@ -1911,10 +1941,10 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L24" s="2" t="s">
         <v>25</v>
@@ -1923,15 +1953,15 @@
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O24" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -1943,13 +1973,13 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>21</v>
@@ -1958,10 +1988,10 @@
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -1970,10 +2000,10 @@
         <v>26</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1989,23 +2019,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2013,16 +2043,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -2033,7 +2063,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>0</v>
+        <v>19.17</v>
       </c>
       <c r="J5" s="4">
         <v>1</v>
@@ -2041,7 +2071,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -2054,7 +2084,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -2062,7 +2092,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -2093,12 +2123,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="B2">
         <v>24</v>
@@ -2112,7 +2142,7 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>0</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
@@ -2122,25 +2152,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -2157,13 +2187,13 @@
         <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -2175,21 +2205,21 @@
         <v>24</v>
       </c>
       <c r="P10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E11">
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H11">
         <v>7</v>
@@ -2201,21 +2231,21 @@
         <v>24</v>
       </c>
       <c r="M11" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="N11">
         <v>0</v>
       </c>
       <c r="P11" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -2227,39 +2257,39 @@
         <v>14</v>
       </c>
       <c r="J12" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="K12">
         <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="Q12">
-        <v>18</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -2267,13 +2297,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H14">
         <v>3</v>
       </c>
       <c r="M14" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -2281,7 +2311,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -2289,7 +2319,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>114</v>
+        <v>124</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -2297,7 +2327,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -2305,10 +2335,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -2316,7 +2346,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -2324,142 +2354,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>15</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>19</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>34</v>
+        <v>85</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>41</v>
+        <v>64</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>73</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>55</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
